--- a/output/roomself_excel/7819.xlsx
+++ b/output/roomself_excel/7819.xlsx
@@ -476,7 +476,7 @@
         <v>3152</v>
       </c>
       <c r="E2" t="n">
-        <v>825</v>
+        <v>406</v>
       </c>
       <c r="F2" t="n">
         <v>391</v>
@@ -498,10 +498,10 @@
         <v>8092</v>
       </c>
       <c r="E3" t="n">
-        <v>977</v>
+        <v>825</v>
       </c>
       <c r="F3" t="n">
-        <v>825</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4">
@@ -542,10 +542,10 @@
         <v>3464</v>
       </c>
       <c r="E5" t="n">
-        <v>576</v>
+        <v>175</v>
       </c>
       <c r="F5" t="n">
-        <v>418</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">

--- a/output/roomself_excel/7819.xlsx
+++ b/output/roomself_excel/7819.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>3152</v>
       </c>
-      <c r="E2" t="n">
-        <v>406</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>391</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>373</v>
+      </c>
+      <c r="J2" t="n">
+        <v>33</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>8092</v>
       </c>
-      <c r="E3" t="n">
-        <v>825</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>572</v>
-      </c>
+        <v>910</v>
+      </c>
+      <c r="G3" t="n">
+        <v>33</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>745</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +592,31 @@
       <c r="D4" t="n">
         <v>2956</v>
       </c>
-      <c r="E4" t="n">
-        <v>406</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>378</v>
+      </c>
+      <c r="J4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +633,23 @@
       <c r="D5" t="n">
         <v>3464</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>175</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>28</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +666,31 @@
       <c r="D6" t="n">
         <v>4476</v>
       </c>
-      <c r="E6" t="n">
-        <v>814</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>389</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="G6" t="n">
+        <v>28</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>734</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +707,23 @@
       <c r="D7" t="n">
         <v>1644</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>205</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>33</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +740,15 @@
       <c r="D8" t="n">
         <v>1380</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +765,38 @@
       <c r="D9" t="n">
         <v>2916</v>
       </c>
-      <c r="E9" t="n">
-        <v>400</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>396</v>
+        <v>368</v>
+      </c>
+      <c r="G9" t="n">
+        <v>28</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>13</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>361</v>
+      </c>
+      <c r="M9" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +814,15 @@
       <c r="D10" t="n">
         <v>1380</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +839,31 @@
       <c r="D11" t="n">
         <v>1632</v>
       </c>
-      <c r="E11" t="n">
-        <v>143</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>134</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>132</v>
+      </c>
+      <c r="J11" t="n">
+        <v>28</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +880,31 @@
       <c r="D12" t="n">
         <v>1452</v>
       </c>
-      <c r="E12" t="n">
-        <v>239</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>190</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="G12" t="n">
+        <v>33</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>206</v>
+      </c>
+      <c r="J12" t="n">
+        <v>33</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +921,23 @@
       <c r="D13" t="n">
         <v>1188</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>140</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>33</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +954,23 @@
       <c r="D14" t="n">
         <v>1028</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>171</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>33</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +987,23 @@
       <c r="D15" t="n">
         <v>1072</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>175</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>28</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,11 +1020,38 @@
       <c r="D16" t="n">
         <v>1844</v>
       </c>
-      <c r="E16" t="n">
-        <v>261</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>242</v>
+        <v>214</v>
+      </c>
+      <c r="G16" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>494</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>214</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/7819.xlsx
+++ b/output/roomself_excel/7819.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,46 @@
           <t>ExtWallWidth_3</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -535,6 +575,26 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>33</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -576,6 +636,38 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>311</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>22</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>90</v>
+      </c>
+      <c r="U3" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -617,6 +709,26 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>28</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -650,6 +762,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -691,6 +811,38 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>28</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>87</v>
+      </c>
+      <c r="U6" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -724,6 +876,26 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>33</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -749,6 +921,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -798,6 +978,26 @@
       <c r="M9" t="n">
         <v>28</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>28</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -823,6 +1023,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -864,6 +1072,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -905,6 +1121,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -938,6 +1162,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -971,6 +1203,26 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>33</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1004,6 +1256,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1053,6 +1313,26 @@
       <c r="M16" t="n">
         <v>20</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>14</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
